--- a/asignaturas/biologia/propuesta/Propuesta_Biologia_G02-G04.xlsx
+++ b/asignaturas/biologia/propuesta/Propuesta_Biologia_G02-G04.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -551,32 +551,32 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>5. Los animales. (después de 5.2; ocupa el número que libera la fusión 3)</t>
+          <t>4. Las plantas. (después de 4.2)</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>5.13. Comparación de las estrategias de reproducción de animales y plantas: huevos, crías vivas, semillas, esquejes y cuidado de las crías.</t>
+          <t>4.10. Descripción de cómo se reproducen las plantas: polinización, formación de semillas y frutos, y propagación por esquejes o tubérculos.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Clasifica en un cuadro animales y plantas de su entorno según cómo se reproducen y explica, con un ejemplo, por qué producir muchos huevos o semillas o cuidar a las crías ayuda a que sobrevivan.</t>
+          <t>Señala en una flor real las partes que intervienen en la polinización, relaciona la flor con el fruto y la semilla, y compara una planta que nace de semilla con otra que nace de un esqueje.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Reproducción sexual y asexual, Ciclo de vida de los animales, Ciclo de vida de las plantas</t>
+          <t>Reproducción sexual de las plantas con flor, Reproducción sexual y asexual, Ciclo de vida de las plantas</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>T4_27-B2.2 Herencia y estrategias de reproducción (reforzar: 0 temas, sin cobertura); SG 5, UY 3 (Reproducción sexual de las plantas con flor); prerrequisito: Reproducción sexual y asexual (hoy en 6.°; bloqueo de la reproducción de plantas con flor)</t>
+          <t>ENG 2, UY 3, SG 5, AU 8 (Reproducción sexual de las plantas con flor); T4_27-B2.2 Herencia y estrategias de reproducción (reforzar: 0 temas, sin cobertura); prerrequisito: Reproducción sexual y asexual (hoy en 6.°; este tema la introduce)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>El objetivo B2.2 no tiene ningún tema en 2.° a 4.°. Se introduce de forma descriptiva tras el ciclo de vida (5.2). Así, la reproducción sexual y asexual llega antes de la fecundación en plantas con flor que la propuesta 5.°–8.° ubica en 5.°. Se paga con la fusión 3.</t>
+          <t>Inglaterra, Uruguay y Singapur enseñan la flor, la semilla y el fruto entre 2.° y 5.°; El Salvador, en 6.°. El tema introduce también la propagación asexual, su bloqueo. Se paga con la fusión 4.</t>
         </is>
       </c>
     </row>
@@ -595,36 +595,36 @@
       </c>
       <c r="E3" s="3" t="n"/>
       <c r="F3" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>6. Cuerpo humano: movimiento e interacciones. (después de 6.10)</t>
+          <t>5. Los animales. (después de 5.2)</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>6.11. Comparación de los rasgos que los descendientes heredan de sus progenitores en plantas, animales y personas.</t>
+          <t>5.14. Comparación de las estrategias de reproducción de los animales: huevos o crías vivas, número de crías y cuidado parental.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Compara rasgos de crías y progenitores (color, forma de hojas, pelaje) a partir de fotografías o de un registro y distingue rasgos heredados de rasgos que dependen del ambiente o de lo aprendido.</t>
+          <t>Clasifica animales de su entorno según cómo nacen y cuántas crías tienen y explica, con un ejemplo, por qué poner muchos huevos o cuidar a las crías ayuda a que sobrevivan.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Herencia de rasgos</t>
+          <t>Estrategias reproductivas y supervivencia de la descendencia, Ciclo de vida de los animales</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>CO 2, SG 5 (Herencia de rasgos; hoy en 10.°); T4_27-B2.2 Herencia y estrategias de reproducción (sin cobertura); bloqueos: ninguno</t>
+          <t>T4_27-B2.2 Herencia y estrategias de reproducción (reforzar: 0 temas, sin cobertura); prerrequisito: Reproducción sexual y asexual (acción 1, mismo grado, unidad anterior)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>La herencia aparece hoy en 10.°. Colombia la trabaja en 2.° y Singapur en 5.°. No tiene prerrequisitos. Cierra la unidad de reproducción humana de 4.° y completa B2.2. Se paga con la fusión 4.</t>
+          <t>Completa la parte de «estrategias de reproducción» del objetivo B2.2, que no tiene ningún tema en 2.° a 4.°. Va después del ciclo de vida (5.2). Se paga con la fusión 5.</t>
         </is>
       </c>
     </row>
@@ -634,51 +634,45 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>G03-CIE-U5-5.12, G03-CIE-U5-5.13</t>
-        </is>
-      </c>
+          <t>nuevo</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
       <c r="D4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5. Los animales.</t>
+          <t>6. Cuerpo humano: movimiento e interacciones. (después de 6.10)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5.12. Relación entre las estructuras del cuerpo de los vertebrados (esqueleto, extremidades, cubierta corporal) y su función.</t>
+          <t>6.11. Comparación de los rasgos que los descendientes heredan de sus progenitores en plantas, animales y personas.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Compara peces, anfibios, reptiles, aves y mamíferos en una tabla y explica, con un ejemplo, cómo la forma de las extremidades o de la cubierta corporal se relaciona con su forma de moverse o de protegerse.</t>
+          <t>Compara rasgos de crías y progenitores (color, forma de hojas, pelaje) en fotografías o en un registro y distingue los rasgos heredados de los que dependen del ambiente o de lo aprendido.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Grupos de vertebrados, Estructuras del cuerpo animal y su función</t>
+          <t>Herencia de rasgos</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Sistema locomotor (4.°) necesita Estructuras del cuerpo animal y su función (hoy sin grado en SV); temas fusionados: G03-5.12 y G03-5.13 (ambos sobre la morfología de vertebrados)</t>
+          <t>CO 2, ENG 4, SG 5 (Herencia de rasgos; hoy en 10.°); T4_27-B2.2 Herencia y estrategias de reproducción (reforzar: 0 temas, sin cobertura); bloqueos: ninguno</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5.12 y 5.13 repiten la descripción de los vertebrados. Unidos y orientados a estructura y función, introducen en 3.° el prerrequisito que le falta al sistema locomotor de 4.°. Libera el espacio del tema nuevo 1.</t>
+          <t>La herencia aparece hoy en 10.°. Colombia la trabaja en 2.°, Inglaterra en 4.° y Singapur en 5.°. No tiene prerrequisitos. Cierra la unidad de reproducción humana de 4.°. Se paga con la fusión 6.</t>
         </is>
       </c>
     </row>
@@ -693,46 +687,46 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>G04-CIE-U2-2.9, G04-CIE-U2-2.10</t>
+          <t>G03-CIE-U5-5.12, G03-CIE-U5-5.13</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2. Nutrición.</t>
+          <t>5. Los animales.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>2.9. Medición y representación de datos antropométricos (peso, talla) para valorar el estado nutricional.</t>
+          <t>5.12. Relación entre las estructuras del cuerpo de los vertebrados (esqueleto, extremidades, cubierta corporal) y su función.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Mide peso y talla con instrumentos sencillos, organiza los datos del grupo en una tabla o gráfico y los relaciona con una alimentación y actividad física saludables.</t>
+          <t>Compara peces, anfibios, reptiles, aves y mamíferos en una tabla y explica, con un ejemplo, cómo la forma de las extremidades o de la cubierta corporal se relaciona con su forma de moverse o de protegerse.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Hábitos de vida saludable</t>
+          <t>Grupos de vertebrados, Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>temas fusionados: G04-2.9 y G04-2.10 (ambos trabajan medidas antropométricas)</t>
+          <t>temas fusionados: G03-5.12 y G03-5.13 (ambos sobre la morfología de vertebrados); corregir_secuencia: Sistema locomotor (4.°) necesita Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Los dos temas trabajan las mismas medidas: uno las toma y otro las representa. Unidos forman una sola práctica. La unidad de Nutrición tiene 12 temas. Libera el espacio del tema nuevo 2.</t>
+          <t>5.12 y 5.13 repiten la descripción de los vertebrados. Unidos y orientados a estructura y función, preparan el sistema locomotor de 4.°. Libera el espacio del tema nuevo 1.</t>
         </is>
       </c>
     </row>
@@ -742,51 +736,51 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>G02-CIE-U6-6.10</t>
+          <t>G04-CIE-U2-2.9, G04-CIE-U2-2.10</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>6. Los microorganismos. (después de 6.1, 6.3 y 6.4)</t>
+          <t>2. Nutrición.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6.10. Explicación de cómo las vacunas ayudan a las defensas del cuerpo a prevenir enfermedades causadas por microorganismos.</t>
+          <t>2.9. Medición y representación de datos antropométricos (peso, talla) para valorar el estado nutricional.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Explica con un esquema sencillo que algunas enfermedades las causan microorganismos y que las vacunas preparan las defensas del cuerpo para enfrentarlos.</t>
+          <t>Mide peso y talla con instrumentos sencillos, organiza los datos del grupo en una tabla o gráfico y los relaciona con una alimentación y actividad física saludables.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Inmunidad activa, pasiva y vacunas, Contagio y prevención de enfermedades, Tipos de patógenos</t>
+          <t>Hábitos de vida saludable</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Inmunidad activa, pasiva y vacunas (2.°) necesita Sistema inmunitario (10.°), brecha 8; prerrequisito disponible: Tipos de patógenos (G03-6.1 y 6.3)</t>
+          <t>temas fusionados: G04-2.9 y G04-2.10 (ambos trabajan medidas antropométricas)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>En 2.° las vacunas llegan antes de que se sepa qué es un patógeno. En 3.° van después de infección y patógenos y se nombran las defensas del cuerpo. El sistema inmunitario formal sigue en 10.° (decisión abierta 2).</t>
+          <t>Los dos temas trabajan las mismas medidas: uno las toma y otro las representa. Unidos forman una sola práctica. Libera el espacio del tema nuevo 2.</t>
         </is>
       </c>
     </row>
@@ -796,51 +790,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>fusionar</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>G03-CIE-U5-5.3</t>
+          <t>G04-CIE-U2-2.4, G04-CIE-U2-2.7</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>5. Los animales.</t>
+          <t>2. Nutrición.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>5.3. Observación y registro de taxismos y de otras conductas que ayudan a los animales a sobrevivir (migración, hibernación, vida en grupo).</t>
+          <t>2.4. Elaboración de menús a partir de la estimación de la cantidad de alimento que cubre los requerimientos nutricionales.</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Registra la respuesta de un animal pequeño (cochinilla, lombriz) a la luz o la humedad y explica cómo esa conducta y otras, como la migración, le ayudan a sobrevivir.</t>
+          <t>Elabora el menú de un día para un niño de su edad, estima las porciones de cada grupo de alimentos y justifica por qué cubre sus necesidades.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos, Adaptaciones conductuales</t>
+          <t>Grupos de alimentos y dieta balanceada, Nutrientes y sus funciones</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>CO 2, SG 6 (Adaptaciones conductuales; hoy en 11.°); bloqueos: ninguno</t>
+          <t>temas fusionados: G04-2.4 y G04-2.7 (ambos trabajan los requerimientos nutricionales)</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Las adaptaciones conductuales aparecen hoy en 11.°. Colombia las enseña en 2.°. El tema de taxismos ya observa conducta animal, así que basta ampliarlo, sin gastar presupuesto.</t>
+          <t>Estimar cantidades y elaborar menús es una misma tarea en dos pasos. La unidad de Nutrición tiene 13 temas y 4.° es el grado más cargado. Libera el espacio del tema nuevo 3.</t>
         </is>
       </c>
     </row>
@@ -850,51 +844,51 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G04-CIE-U3-3.6, G04-CIE-U3-3.8</t>
+          <t>G04-CIE-U6-6.6</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>4</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>3. Naturaleza y sus interacciones.</t>
+          <t>4. Seres vivos. (después de 1.9 y 4.8)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3.6. Representación de las interacciones entre seres vivos de la misma especie y de especies distintas: competencia por recursos, depredación y simbiosis. | 3.8. Indagación de los conceptos de hábitat y nicho ecológico como el lugar y el papel de cada especie en el ecosistema.</t>
+          <t>4.15. Experimentación con los órganos de los sentidos y la información que nos dan sobre el entorno.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Representa en un esquema de un ecosistema local al menos una relación de competencia, una de depredación y una de simbiosis, y distingue las que ocurren entre individuos de la misma especie. | Describe el hábitat y el papel (qué come, quién lo come, qué hace en el ecosistema) de dos especies locales.</t>
+          <t>Relaciona cada órgano de los sentidos con el estímulo que capta mediante juegos de identificación (sabores, texturas, sonidos) y propone cómo cuidarlos.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Competencia por recursos, Relaciones intraespecíficas, Simbiosis: mutualismo, comensalismo y parasitismo, Hábitat y ecosistemas comunes, Nicho ecológico y exclusión competitiva</t>
+          <t>Órganos de los sentidos</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Nicho ecológico (4.°) necesita Competencia por recursos (dato: 7.°), brecha 3; CO 3, UY 6 (Relaciones intraespecíficas; Simbiosis)</t>
+          <t>CO 2, ENG 2, UY 3 (Órganos de los sentidos; hoy en 4.°); prerrequisito: Respuesta de los seres vivos a estímulos (G02-1.9); prerrequisito: Estructuras del cuerpo animal y su función (acción 9)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Se hace explícita la competencia en 3.6, antes del nicho en 3.8. El nicho se limita al «papel de la especie»; la exclusión competitiva sigue en 7.°. Se agregan relaciones intraespecíficas (CO 3).</t>
+          <t>Los tres países enseñan los sentidos en 2.° o 3.°. En 2.° se une a la respuesta a estímulos (1.9) y a la relación estructura y función (4.8). Además, alivia 4.°.</t>
         </is>
       </c>
     </row>
@@ -904,51 +898,51 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>revisar</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>G04-CIE-U3-3.3</t>
+          <t>G02-CIE-U6-6.10</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>3. Naturaleza y sus interacciones.</t>
+          <t>6. Los microorganismos. (después de 6.1, 6.3 y 6.4)</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>3.3. Caracterización de los niveles de organización ecológica: organismo, población, comunidad y ecosistema.</t>
+          <t>6.10. Explicación de cómo las vacunas ayudan a las defensas del cuerpo a prevenir enfermedades causadas por microorganismos.</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Ordena en un esquema de un ecosistema local un organismo, su población, la comunidad y el ecosistema, y da un ejemplo de cada nivel.</t>
+          <t>Explica con un esquema sencillo que algunas enfermedades las causan microorganismos y que las vacunas preparan las defensas del cuerpo para enfrentarlos.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Inmunidad activa, pasiva y vacunas, Contagio y prevención de enfermedades, Tipos de patógenos</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Niveles de organización (4.°) necesita La célula como unidad de la vida (6.°), brecha 2; CO 4, SG 5, UY 4 (La célula como unidad de la vida)</t>
+          <t>corregir_secuencia: Inmunidad activa, pasiva y vacunas (2.°) necesita Sistema inmunitario (10.°), brecha 8; prerrequisito disponible: Tipos de patógenos (G03-6.1 y 6.3)</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>El tema trata la organización ecológica, que empieza en el organismo y no requiere la célula. Se precisa la redacción para que no anticipe los niveles celulares. La célula se adelanta a 5.° en la propuesta 5.°–8.°.</t>
+          <t>En 2.° las vacunas llegan antes de que se sepa qué es un patógeno. En 3.° van después de infección y patógenos. El sistema inmunitario formal sigue en 10.° (decisión abierta 2).</t>
         </is>
       </c>
     </row>
@@ -963,46 +957,46 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>G03-CIE-U6-6.7</t>
+          <t>G02-CIE-U4-4.8</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6. Los microorganismos.</t>
+          <t>4. Seres vivos.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6.7. Experimentación con el tiempo de degradación de residuos y alimentos por acción de hongos y bacterias.</t>
+          <t>4.8. Relación de las partes del cuerpo de un animal (patas, pico, dientes, cubierta) con su función, su alimentación y su hábitat.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Compara durante dos semanas cómo se degradan restos de alimentos, papel y plástico, registra los cambios y explica qué organismos los producen.</t>
+          <t>Explica con dibujos cómo una parte del cuerpo de tres animales de su entorno les sirve para moverse, alimentarse o protegerse.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Microorganismos</t>
+          <t>Estructuras del cuerpo animal y su función, Adaptaciones estructurales, Hábitat y ecosistemas comunes</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Productores, consumidores y descomponedores (3.°) necesita Cadena alimentaria (4.°), brecha 1</t>
+          <t>corregir_secuencia: Sistema locomotor (4.°) necesita Estructuras del cuerpo animal y su función (sin grado en SV); bloqueo de Órganos de los sentidos (acción 7)</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>La degradación se trabaja como acción de microorganismos. El papel de los descomponedores en la cadena se nombra en 4.°, en 3.7, después de la cadena alimentaria. No cambia el presupuesto.</t>
+          <t>El tema ya relaciona el cuerpo del animal con su entorno. Se hace explícita la relación estructura y función, que hoy no tiene grado y bloquea los sentidos y el sistema locomotor.</t>
         </is>
       </c>
     </row>
@@ -1017,11 +1011,11 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>G03-CIE-U5-5.6, G03-CIE-U5-5.7, G03-CIE-U5-5.8, G03-CIE-U5-5.9, G03-CIE-U5-5.10, G03-CIE-U5-5.11, G03-CIE-U4-4.8, G03-CIE-U4-4.9, G04-CIE-U2-2.4, G04-CIE-U2-2.7</t>
+          <t>G03-CIE-U5-5.3</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E11" s="3" t="n">
         <v>3</v>
@@ -1031,32 +1025,248 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5. Los animales. / 4. Las plantas. (3.°); 2. Nutrición. (4.°)</t>
+          <t>5. Los animales.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
+          <t>5.3. Observación y registro de taxismos y de otras conductas que ayudan a los animales a sobrevivir (migración, hibernación, vida en grupo).</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>Registra la respuesta de un animal pequeño (cochinilla, lombriz) a la luz o la humedad y explica cómo esa conducta y otras, como la migración, le ayudan a sobrevivir.</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Respuesta de los seres vivos a estímulos, Adaptaciones conductuales</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>CO 2, AU 4, SG 6 (Adaptaciones conductuales; hoy en 11.°); bloqueos: ninguno</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>Las adaptaciones conductuales aparecen hoy en 11.°. Colombia las enseña en 2.° y Australia en 4.°. El tema de taxismos ya observa conducta animal, así que basta ampliarlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>G04-CIE-U3-3.7, G04-CIE-U3-3.6, G04-CIE-U3-3.8</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>3. Naturaleza y sus interacciones. (se reordena: cadenas tróficas antes que interacciones)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3.6. Representación de cadenas tróficas acuáticas y terrestres con productores, consumidores y descomponedores. | 3.7. Representación de las interacciones entre seres vivos de la misma especie y de especies distintas: competencia por recursos, depredación y simbiosis. | 3.8. Indagación de los conceptos de hábitat y nicho ecológico como el lugar y el papel de cada especie en el ecosistema.</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Construye una cadena trófica de un ecosistema local e indica el papel de los descomponedores. | Representa en un esquema al menos una relación de competencia, una de depredación y una de simbiosis, y distingue las que ocurren entre individuos de la misma especie. | Describe el hábitat y el papel (qué come, quién lo come, qué hace en el ecosistema) de dos especies locales.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Cadena alimentaria, Productores, consumidores y descomponedores, Competencia por recursos, Depredación, Relaciones intraespecíficas, Simbiosis: mutualismo, comensalismo y parasitismo, Nicho ecológico y exclusión competitiva</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>CO 3, ENG 6 (Competencia por recursos); ENG 2, CO 3 (Depredación; bloqueo: Cadena alimentaria); CO 3, UY 6 (Relaciones intraespecíficas); corregir_secuencia: Nicho ecológico necesita Competencia por recursos</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Se enseña primero la cadena trófica, bloqueo de la depredación. Después vienen las interacciones, con competencia y depredación explícitas, y al final el nicho, como «papel de la especie». La exclusión competitiva sigue en 7.°.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>G04-CIE-U3-3.3</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>3. Naturaleza y sus interacciones.</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>3.3. Caracterización de los niveles de organización ecológica: organismo, población, comunidad y ecosistema.</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Ordena en un esquema de un ecosistema local un organismo, su población, la comunidad y el ecosistema, y da un ejemplo de cada nivel.</t>
+        </is>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Niveles de organización de los seres vivos</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>corregir_secuencia: Niveles de organización (4.°) necesita La célula como unidad de la vida (6.°), brecha 2</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>El tema trata la organización ecológica, que empieza en el organismo y no requiere la célula. Se precisa la redacción. La célula se adelanta a 5.° en la propuesta 5.°–8.°.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>G03-CIE-U6-6.7, G03-CIE-U6-6.8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6. Los microorganismos.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6.7. Experimentación con el tiempo de degradación de residuos y alimentos por acción de hongos y bacterias. | 6.8. Reconocimiento de alimentos que se elaboran con ayuda de microorganismos (pan, yogur, queso, encurtidos).</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Compara durante dos semanas cómo se degradan restos de alimentos, papel y plástico, registra los cambios y explica qué organismos los producen. | Prepara o describe la elaboración de un alimento con levadura o bacterias y explica qué cambio observable producen los microorganismos.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Microorganismos, Biotecnología microbiana</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>corregir_secuencia: Productores, consumidores y descomponedores (3.°) necesita Cadena alimentaria (4.°), brecha 1; corregir_secuencia: Fermentación y respiración anaerobia (3.°) necesita Glucólisis… (10.°), brecha 7</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Ambos temas se quedan en lo observable, la acción de los microorganismos. Los descomponedores se nombran en 4.° (acción 11). El mecanismo de la fermentación sigue en Bachillerato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>G03-CIE-U5-5.6, G03-CIE-U5-5.7, G03-CIE-U5-5.8, G03-CIE-U5-5.9, G03-CIE-U5-5.10, G03-CIE-U5-5.11, G03-CIE-U4-4.7, G03-CIE-U4-4.8, G03-CIE-U4-4.9</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>5. Los animales. / 4. Las plantas.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
           <t>Sin redacción nueva: candidatos a consolidar si el MINED decide reducir el peso de Biología en 2.° a 4.°.</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
+      <c r="I15" s="3" t="inlineStr">
         <is>
           <t>No aplica.</t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>Invertebrados e insectos, Tropismos y hormonas vegetales, Grupos de alimentos y dieta balanceada</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t>temas_por_grado: Biología tiene 98 temas en 2.° a 4.°; 6 temas de 3.° sobre grupos de invertebrados (5.6 a 5.11); 3 sobre tropismos y nastias (4.7 a 4.9); 2.4 y 2.7 sobre requerimientos nutricionales</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t>Son grupos de temas que repiten un mismo concepto con detalle taxonómico o práctico alto para la edad. No se fusionan ahora porque el presupuesto ya cuadra. Se señalan por si el MINED decide liberar horas para otras disciplinas (decisión abierta 1).</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Invertebrados e insectos, Tropismos y hormonas vegetales</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>6 temas de 3.° sobre grupos de invertebrados (5.6 a 5.11); 3 temas sobre tropismos y nastias (4.7 a 4.9)</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>Repiten un mismo concepto con un detalle taxonómico o práctico alto para la edad. No se fusionan ahora porque el presupuesto ya cuadra. Quedan como opción si el MINED pasa horas a otras disciplinas (decisión abierta 1).</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1332,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1145,7 +1355,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D3" s="4">
         <f>C3-B3</f>
@@ -1165,10 +1375,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>

--- a/asignaturas/biologia/propuesta/Propuesta_Biologia_G02-G04.xlsx
+++ b/asignaturas/biologia/propuesta/Propuesta_Biologia_G02-G04.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -571,12 +571,12 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>ENG 2, UY 3, SG 5, AU 8 (Reproducción sexual de las plantas con flor); T4_27-B2.2 Herencia y estrategias de reproducción (reforzar: 0 temas, sin cobertura); prerrequisito: Reproducción sexual y asexual (hoy en 6.°; este tema la introduce)</t>
+          <t>ENG 2, UY 3, JP 4, SG 5, AU 8 (Reproducción sexual de las plantas con flor; hoy en 6.°, destino 4); bloqueo: Reproducción sexual y asexual (hoy en 6.°; este tema la introduce)</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>Inglaterra, Uruguay y Singapur enseñan la flor, la semilla y el fruto entre 2.° y 5.°; El Salvador, en 6.°. El tema introduce también la propagación asexual, su bloqueo. Se paga con la fusión 4.</t>
+          <t>Inglaterra (2.°), Uruguay (3.°) y Japón (4.°) enseñan flor, semilla y fruto antes que El Salvador (6.°). Se ubica en 3.° porque ahí está la unidad de plantas. Introduce su bloqueo. Se paga con la fusión 2.</t>
         </is>
       </c>
     </row>
@@ -586,45 +586,51 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr"/>
+          <t>fusionar</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>G03-CIE-U5-5.12, G03-CIE-U5-5.13</t>
+        </is>
+      </c>
       <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>3</v>
+      </c>
       <c r="F3" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5. Los animales. (después de 5.2)</t>
+          <t>5. Los animales.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>5.14. Comparación de las estrategias de reproducción de los animales: huevos o crías vivas, número de crías y cuidado parental.</t>
+          <t>5.12. Relación entre las estructuras del cuerpo de los vertebrados (esqueleto, extremidades, cubierta corporal) y su función.</t>
         </is>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>Clasifica animales de su entorno según cómo nacen y cuántas crías tienen y explica, con un ejemplo, por qué poner muchos huevos o cuidar a las crías ayuda a que sobrevivan.</t>
+          <t>Compara peces, anfibios, reptiles, aves y mamíferos en una tabla y explica, con un ejemplo, cómo la forma de las extremidades o de la cubierta corporal se relaciona con su forma de moverse o de protegerse.</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>Estrategias reproductivas y supervivencia de la descendencia, Ciclo de vida de los animales</t>
+          <t>Grupos de vertebrados, Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>T4_27-B2.2 Herencia y estrategias de reproducción (reforzar: 0 temas, sin cobertura); prerrequisito: Reproducción sexual y asexual (acción 1, mismo grado, unidad anterior)</t>
+          <t>temas fusionados: G03-5.12 y G03-5.13 (ambos sobre la morfología de vertebrados); corregir_secuencia: Sistema locomotor (4.°) necesita Estructuras del cuerpo animal y su función (sin grado en SV)</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>Completa la parte de «estrategias de reproducción» del objetivo B2.2, que no tiene ningún tema en 2.° a 4.°. Va después del ciclo de vida (5.2). Se paga con la fusión 5.</t>
+          <t>5.12 y 5.13 repiten la descripción de los vertebrados. Unidos y orientados a estructura y función, preparan el sistema locomotor de 4.°. Libera el espacio del tema nuevo 1.</t>
         </is>
       </c>
     </row>
@@ -634,45 +640,51 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>nuevo</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr"/>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>G04-CIE-U3-3.7</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n"/>
+        <v>1</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="F4" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6. Cuerpo humano: movimiento e interacciones. (después de 6.10)</t>
+          <t>5. Los animales. (después de 5.4)</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6.11. Comparación de los rasgos que los descendientes heredan de sus progenitores en plantas, animales y personas.</t>
+          <t>5.14. Representación de cadenas tróficas acuáticas y terrestres: productores, consumidores (presas y depredadores) y descomponedores.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Compara rasgos de crías y progenitores (color, forma de hojas, pelaje) en fotografías o en un registro y distingue los rasgos heredados de los que dependen del ambiente o de lo aprendido.</t>
+          <t>Construye una cadena trófica de un ecosistema local con al menos cuatro eslabones, señala una presa y su depredador y explica qué ocurre con los restos gracias a los descomponedores.</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>Herencia de rasgos</t>
+          <t>Cadena alimentaria, Productores, consumidores y descomponedores, Depredación</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>CO 2, ENG 4, SG 5 (Herencia de rasgos; hoy en 10.°); T4_27-B2.2 Herencia y estrategias de reproducción (reforzar: 0 temas, sin cobertura); bloqueos: ninguno</t>
+          <t>ENG 2, CO 3, JP 5 (Depredación; hoy en 7.°, destino 3; bloqueo: Cadena alimentaria, hoy en 4.°); corregir_secuencia: Productores, consumidores y descomponedores (3.°) necesita Cadena alimentaria (4.°), brecha 1; prerrequisito disponible: Nutrición autótrofa y heterótrofa (G03-5.4, misma unidad)</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>La herencia aparece hoy en 10.°. Colombia la trabaja en 2.°, Inglaterra en 4.° y Singapur en 5.°. No tiene prerrequisitos. Cierra la unidad de reproducción humana de 4.°. Se paga con la fusión 6.</t>
+          <t>La cadena trófica es el bloqueo de la depredación (destino 3) y debe ir antes de la degradación por descomponedores (G03-6.7). En 3.° sigue a las formas de nutrición (5.4). Alivia 4.°.</t>
         </is>
       </c>
     </row>
@@ -682,51 +694,51 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>mover</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>G03-CIE-U5-5.12, G03-CIE-U5-5.13</t>
+          <t>G02-CIE-U6-6.10</t>
         </is>
       </c>
       <c r="D5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>3</v>
-      </c>
       <c r="F5" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>5. Los animales.</t>
+          <t>6. Los microorganismos. (después de 6.1, 6.3 y 6.4)</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>5.12. Relación entre las estructuras del cuerpo de los vertebrados (esqueleto, extremidades, cubierta corporal) y su función.</t>
+          <t>6.10. Explicación de cómo las vacunas ayudan a las defensas del cuerpo a prevenir enfermedades causadas por microorganismos.</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Compara peces, anfibios, reptiles, aves y mamíferos en una tabla y explica, con un ejemplo, cómo la forma de las extremidades o de la cubierta corporal se relaciona con su forma de moverse o de protegerse.</t>
+          <t>Explica con un esquema sencillo que algunas enfermedades las causan microorganismos y que las vacunas preparan las defensas del cuerpo para enfrentarlos.</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Grupos de vertebrados, Estructuras del cuerpo animal y su función</t>
+          <t>Inmunidad activa, pasiva y vacunas, Contagio y prevención de enfermedades, Tipos de patógenos</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>temas fusionados: G03-5.12 y G03-5.13 (ambos sobre la morfología de vertebrados); corregir_secuencia: Sistema locomotor (4.°) necesita Estructuras del cuerpo animal y su función</t>
+          <t>corregir_secuencia: Inmunidad activa, pasiva y vacunas (2.°) necesita Sistema inmunitario (10.°), brecha 8; prerrequisito disponible: Tipos de patógenos (G03-6.1 y 6.3)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>5.12 y 5.13 repiten la descripción de los vertebrados. Unidos y orientados a estructura y función, preparan el sistema locomotor de 4.°. Libera el espacio del tema nuevo 1.</t>
+          <t>En 2.° las vacunas llegan antes de que se sepa qué es un patógeno. En 3.° van después de infección y patógenos. El sistema inmunitario formal sigue en 10.° (decisión abierta 2).</t>
         </is>
       </c>
     </row>
@@ -736,51 +748,51 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>G04-CIE-U2-2.9, G04-CIE-U2-2.10</t>
+          <t>G02-CIE-U4-4.8</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>4</v>
-      </c>
       <c r="F6" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2. Nutrición.</t>
+          <t>4. Seres vivos.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2.9. Medición y representación de datos antropométricos (peso, talla) para valorar el estado nutricional.</t>
+          <t>4.8. Relación de las partes del cuerpo de un animal (patas, pico, dientes, cubierta) con su función, su alimentación y su hábitat.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Mide peso y talla con instrumentos sencillos, organiza los datos del grupo en una tabla o gráfico y los relaciona con una alimentación y actividad física saludables.</t>
+          <t>Explica con dibujos cómo una parte del cuerpo de tres animales de su entorno les sirve para moverse, alimentarse o protegerse.</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>Hábitos de vida saludable</t>
+          <t>Estructuras del cuerpo animal y su función, Adaptaciones estructurales, Hábitat y ecosistemas comunes</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>temas fusionados: G04-2.9 y G04-2.10 (ambos trabajan medidas antropométricas)</t>
+          <t>corregir_secuencia: Sistema locomotor (4.°) necesita Estructuras del cuerpo animal y su función (sin grado en SV)</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>Los dos temas trabajan las mismas medidas: uno las toma y otro las representa. Unidos forman una sola práctica. Libera el espacio del tema nuevo 2.</t>
+          <t>El tema ya relaciona el cuerpo del animal con su entorno. Se hace explícita la relación estructura y función, que hoy no tiene grado y es prerrequisito del sistema locomotor de 4.°.</t>
         </is>
       </c>
     </row>
@@ -790,51 +802,51 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>fusionar</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>G04-CIE-U2-2.4, G04-CIE-U2-2.7</t>
+          <t>G03-CIE-U5-5.3</t>
         </is>
       </c>
       <c r="D7" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2. Nutrición.</t>
+          <t>5. Los animales.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>2.4. Elaboración de menús a partir de la estimación de la cantidad de alimento que cubre los requerimientos nutricionales.</t>
+          <t>5.3. Observación y registro de taxismos y de otras conductas que ayudan a los animales a sobrevivir según la estación (migración, hibernación, vida en grupo).</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Elabora el menú de un día para un niño de su edad, estima las porciones de cada grupo de alimentos y justifica por qué cubre sus necesidades.</t>
+          <t>Registra la respuesta de un animal pequeño (cochinilla, lombriz) a la luz o la humedad y explica cómo esa conducta y otras, como la migración o la hibernación, le ayudan a sobrevivir.</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>Grupos de alimentos y dieta balanceada, Nutrientes y sus funciones</t>
+          <t>Respuesta de los seres vivos a estímulos, Adaptaciones conductuales</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>temas fusionados: G04-2.4 y G04-2.7 (ambos trabajan los requerimientos nutricionales)</t>
+          <t>CO 2, JP 3, AU 4, SG 6 (Adaptaciones conductuales; hoy en 11.°, destino 4); bloqueos: ninguno</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Estimar cantidades y elaborar menús es una misma tarea en dos pasos. La unidad de Nutrición tiene 13 temas y 4.° es el grado más cargado. Libera el espacio del tema nuevo 3.</t>
+          <t>Las adaptaciones conductuales aparecen hoy en 11.°. Japón las trabaja en 3.° y Australia en 4.°. El tema de taxismos ya observa conducta animal, así que basta ampliarlo.</t>
         </is>
       </c>
     </row>
@@ -844,51 +856,51 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>G04-CIE-U6-6.6</t>
+          <t>G03-CIE-U5-5.2</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>4. Seres vivos. (después de 1.9 y 4.8)</t>
+          <t>5. Los animales.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4.15. Experimentación con los órganos de los sentidos y la información que nos dan sobre el entorno.</t>
+          <t>5.2. Reconocimiento de las etapas de desarrollo de los animales y de sus estrategias de reproducción: huevos o crías vivas, número de crías y cuidado parental.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Relaciona cada órgano de los sentidos con el estímulo que capta mediante juegos de identificación (sabores, texturas, sonidos) y propone cómo cuidarlos.</t>
+          <t>Ordena las etapas del ciclo de vida de dos animales de su entorno, los clasifica según nazcan de huevo o vivos, y explica con un ejemplo por qué tener muchas crías o cuidarlas ayuda a que sobrevivan.</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>Órganos de los sentidos</t>
+          <t>Ciclo de vida de los animales, Estrategias reproductivas y supervivencia de la descendencia</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>CO 2, ENG 2, UY 3 (Órganos de los sentidos; hoy en 4.°); prerrequisito: Respuesta de los seres vivos a estímulos (G02-1.9); prerrequisito: Estructuras del cuerpo animal y su función (acción 9)</t>
+          <t>reforzar: T4_27-B2.2 Herencia y estrategias de reproducción (0 temas, sin cobertura); prerrequisito disponible: Ciclo de vida de los animales (mismo tema)</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>Los tres países enseñan los sentidos en 2.° o 3.°. En 2.° se une a la respuesta a estímulos (1.9) y a la relación estructura y función (4.8). Además, alivia 4.°.</t>
+          <t>B2.2 es el único objetivo del marco de 4.° sin ningún tema en el ciclo. Ampliar el tema del ciclo de vida cubre las estrategias de reproducción sin gastar presupuesto. La herencia de rasgos se resuelve en 5.°–8.° (destino 5).</t>
         </is>
       </c>
     </row>
@@ -898,51 +910,51 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>mover</t>
+          <t>revisar</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>G02-CIE-U6-6.10</t>
+          <t>G03-CIE-U5-5.4</t>
         </is>
       </c>
       <c r="D9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>6. Los microorganismos. (después de 6.1, 6.3 y 6.4)</t>
+          <t>5. Los animales.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>6.10. Explicación de cómo las vacunas ayudan a las defensas del cuerpo a prevenir enfermedades causadas por microorganismos.</t>
+          <t>5.4. Clasificación de las formas de nutrición de los animales y de los órganos con que respiran (pulmones, branquias, piel).</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Explica con un esquema sencillo que algunas enfermedades las causan microorganismos y que las vacunas preparan las defensas del cuerpo para enfrentarlos.</t>
+          <t>Clasifica animales de su entorno según lo que comen y según el órgano con que respiran, y relaciona ese órgano con el medio en que viven.</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>Inmunidad activa, pasiva y vacunas, Contagio y prevención de enfermedades, Tipos de patógenos</t>
+          <t>Nutrición autótrofa y heterótrofa, Estructuras del cuerpo animal y su función</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Inmunidad activa, pasiva y vacunas (2.°) necesita Sistema inmunitario (10.°), brecha 8; prerrequisito disponible: Tipos de patógenos (G03-6.1 y 6.3)</t>
+          <t>corregir_secuencia: Intercambio de gases en animales (3.°) necesita Sistema respiratorio (4.°), brecha 1</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>En 2.° las vacunas llegan antes de que se sepa qué es un patógeno. En 3.° van después de infección y patógenos. El sistema inmunitario formal sigue en 10.° (decisión abierta 2).</t>
+          <t>En 3.° basta reconocer los órganos con que respiran los animales. El intercambio de gases se deja para después del sistema respiratorio de 4.°. 5.4 queda como prerrequisito de la cadena trófica (acción 3).</t>
         </is>
       </c>
     </row>
@@ -957,46 +969,46 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>G02-CIE-U4-4.8</t>
+          <t>G03-CIE-U6-6.7, G03-CIE-U6-6.8</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4. Seres vivos.</t>
+          <t>6. Los microorganismos.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4.8. Relación de las partes del cuerpo de un animal (patas, pico, dientes, cubierta) con su función, su alimentación y su hábitat.</t>
+          <t>6.7. Experimentación con el tiempo de degradación de residuos y alimentos por acción de hongos y bacterias descomponedores. | 6.8. Reconocimiento de alimentos que se elaboran con ayuda de microorganismos (pan, yogur, queso, encurtidos).</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Explica con dibujos cómo una parte del cuerpo de tres animales de su entorno les sirve para moverse, alimentarse o protegerse.</t>
+          <t>Compara durante dos semanas cómo se degradan restos de alimentos, papel y plástico, registra los cambios y explica qué organismos los producen. | Prepara o describe la elaboración de un alimento con levadura o bacterias y explica qué cambio observable producen los microorganismos.</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Estructuras del cuerpo animal y su función, Adaptaciones estructurales, Hábitat y ecosistemas comunes</t>
+          <t>Microorganismos, Productores, consumidores y descomponedores, Biotecnología microbiana</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Sistema locomotor (4.°) necesita Estructuras del cuerpo animal y su función (sin grado en SV); bloqueo de Órganos de los sentidos (acción 7)</t>
+          <t>corregir_secuencia: Productores, consumidores y descomponedores (3.°) necesita Cadena alimentaria (4.°), brecha 1; resuelta con la acción 3; corregir_secuencia: Fermentación y respiración anaerobia (3.°) necesita Glucólisis, ciclo de Krebs y cadena respiratoria (10.°), brecha 7</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>El tema ya relaciona el cuerpo del animal con su entorno. Se hace explícita la relación estructura y función, que hoy no tiene grado y bloquea los sentidos y el sistema locomotor.</t>
+          <t>La degradación llega después de la cadena trófica (acción 3, unidad 5) y nombra a los descomponedores. Los alimentos fermentados se quedan en lo observable; el mecanismo de la fermentación sigue en Bachillerato.</t>
         </is>
       </c>
     </row>
@@ -1011,46 +1023,46 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>G03-CIE-U5-5.3</t>
+          <t>G04-CIE-U3-3.3</t>
         </is>
       </c>
       <c r="D11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>5. Los animales.</t>
+          <t>3. Naturaleza y sus interacciones.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>5.3. Observación y registro de taxismos y de otras conductas que ayudan a los animales a sobrevivir (migración, hibernación, vida en grupo).</t>
+          <t>3.3. Caracterización de los niveles de organización ecológica: organismo, población, comunidad y ecosistema.</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>Registra la respuesta de un animal pequeño (cochinilla, lombriz) a la luz o la humedad y explica cómo esa conducta y otras, como la migración, le ayudan a sobrevivir.</t>
+          <t>Ordena en un esquema de un ecosistema local un organismo, su población, la comunidad y el ecosistema, y da un ejemplo de cada nivel.</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Respuesta de los seres vivos a estímulos, Adaptaciones conductuales</t>
+          <t>Niveles de organización de los seres vivos</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>CO 2, AU 4, SG 6 (Adaptaciones conductuales; hoy en 11.°); bloqueos: ninguno</t>
+          <t>corregir_secuencia: Niveles de organización de los seres vivos (4.°) necesita La célula como unidad de la vida (6.°), brecha 2</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>Las adaptaciones conductuales aparecen hoy en 11.°. Colombia las enseña en 2.° y Australia en 4.°. El tema de taxismos ya observa conducta animal, así que basta ampliarlo.</t>
+          <t>El tema trata la organización ecológica, que empieza en el organismo y no requiere la célula. Se precisa la redacción. La célula se adelanta en la propuesta 5.°–8.°.</t>
         </is>
       </c>
     </row>
@@ -1065,11 +1077,11 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>G04-CIE-U3-3.7, G04-CIE-U3-3.6, G04-CIE-U3-3.8</t>
+          <t>G04-CIE-U5-5.2</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>4</v>
@@ -1079,32 +1091,32 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3. Naturaleza y sus interacciones. (se reordena: cadenas tróficas antes que interacciones)</t>
+          <t>5. Cuerpo humano: materia y energía.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3.6. Representación de cadenas tróficas acuáticas y terrestres con productores, consumidores y descomponedores. | 3.7. Representación de las interacciones entre seres vivos de la misma especie y de especies distintas: competencia por recursos, depredación y simbiosis. | 3.8. Indagación de los conceptos de hábitat y nicho ecológico como el lugar y el papel de cada especie en el ecosistema.</t>
+          <t>5.2. Construcción de un modelo del recorrido de los alimentos: cómo la boca, el estómago y el intestino los trituran y deshacen hasta que los nutrientes pasan a la sangre.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Construye una cadena trófica de un ecosistema local e indica el papel de los descomponedores. | Representa en un esquema al menos una relación de competencia, una de depredación y una de simbiosis, y distingue las que ocurren entre individuos de la misma especie. | Describe el hábitat y el papel (qué come, quién lo come, qué hace en el ecosistema) de dos especies locales.</t>
+          <t>Usa un modelo sencillo (bolsa, galleta, agua, media) para mostrar cómo el alimento se tritura y se deshace, e indica en qué órgano los nutrientes pasan a la sangre.</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>Cadena alimentaria, Productores, consumidores y descomponedores, Competencia por recursos, Depredación, Relaciones intraespecíficas, Simbiosis: mutualismo, comensalismo y parasitismo, Nicho ecológico y exclusión competitiva</t>
+          <t>Sistema digestivo, Nutrientes y sus funciones</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>CO 3, ENG 6 (Competencia por recursos); ENG 2, CO 3 (Depredación; bloqueo: Cadena alimentaria); CO 3, UY 6 (Relaciones intraespecíficas); corregir_secuencia: Nicho ecológico necesita Competencia por recursos</t>
+          <t>ENG 4, SG 4, UY 4, JP 5 (Digestión química y absorción de nutrientes; hoy en 8.°, destino 4); bloqueo: Enzimas (6.°); no se adelanta</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>Se enseña primero la cadena trófica, bloqueo de la depredación. Después vienen las interacciones, con competencia y depredación explícitas, y al final el nicho, como «papel de la especie». La exclusión competitiva sigue en 7.°.</t>
+          <t>Tres países de alto desempeño enseñan digestión y absorción entre 4.° y 5.°. Las enzimas, su bloqueo, llegan en 6.°, así que el modelo prepara la idea sin nombrarlas. Sustituye un modelo puramente anatómico.</t>
         </is>
       </c>
     </row>
@@ -1119,11 +1131,11 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>G04-CIE-U3-3.3</t>
+          <t>G04-CIE-U2-2.4, G04-CIE-U2-2.7, G04-CIE-U2-2.9, G04-CIE-U2-2.10</t>
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E13" s="3" t="n">
         <v>4</v>
@@ -1133,32 +1145,32 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>3. Naturaleza y sus interacciones.</t>
+          <t>2. Nutrición.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>3.3. Caracterización de los niveles de organización ecológica: organismo, población, comunidad y ecosistema.</t>
+          <t>Sin redacción nueva: pares candidatos a fusionar si el MINED necesita espacio en 4.° (2.4 con 2.7; 2.9 con 2.10).</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>Ordena en un esquema de un ecosistema local un organismo, su población, la comunidad y el ecosistema, y da un ejemplo de cada nivel.</t>
+          <t>No aplica.</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Grupos de alimentos y dieta balanceada, Hábitos de vida saludable</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Niveles de organización (4.°) necesita La célula como unidad de la vida (6.°), brecha 2</t>
+          <t>temas_por_grado: 4.° tiene 40 temas de Biología (40 % del ciclo); 2.4 y 2.7 trabajan los requerimientos nutricionales; 2.9 y 2.10, las medidas antropométricas</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>El tema trata la organización ecológica, que empieza en el organismo y no requiere la célula. Se precisa la redacción. La célula se adelanta a 5.° en la propuesta 5.°–8.°.</t>
+          <t>En v2 estas fusiones pagaban dos temas nuevos que la evidencia ya no respalda. Sin tema nuevo que pagar, fusionarlas rompería el presupuesto. Quedan señaladas para aliviar 4.° (decisión abierta 1).</t>
         </is>
       </c>
     </row>
@@ -1173,11 +1185,11 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>G03-CIE-U6-6.7, G03-CIE-U6-6.8</t>
+          <t>G03-CIE-U5-5.6, G03-CIE-U5-5.7, G03-CIE-U5-5.8, G03-CIE-U5-5.9, G03-CIE-U5-5.10, G03-CIE-U5-5.11, G03-CIE-U4-4.7, G03-CIE-U4-4.8, G03-CIE-U4-4.9</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>3</v>
@@ -1187,84 +1199,30 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>6. Los microorganismos.</t>
+          <t>5. Los animales. / 4. Las plantas.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6.7. Experimentación con el tiempo de degradación de residuos y alimentos por acción de hongos y bacterias. | 6.8. Reconocimiento de alimentos que se elaboran con ayuda de microorganismos (pan, yogur, queso, encurtidos).</t>
+          <t>Sin redacción nueva: candidatos a consolidar si el MINED decide reducir el peso de Biología en 2.° a 4.°.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Compara durante dos semanas cómo se degradan restos de alimentos, papel y plástico, registra los cambios y explica qué organismos los producen. | Prepara o describe la elaboración de un alimento con levadura o bacterias y explica qué cambio observable producen los microorganismos.</t>
+          <t>No aplica.</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Microorganismos, Biotecnología microbiana</t>
+          <t>Invertebrados e insectos, Tropismos y hormonas vegetales</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Productores, consumidores y descomponedores (3.°) necesita Cadena alimentaria (4.°), brecha 1; corregir_secuencia: Fermentación y respiración anaerobia (3.°) necesita Glucólisis… (10.°), brecha 7</t>
+          <t>6 temas de 3.° sobre grupos de invertebrados (5.6 a 5.11); 3 temas sobre tropismos y nastias (4.7 a 4.9)</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>Ambos temas se quedan en lo observable, la acción de los microorganismos. Los descomponedores se nombran en 4.° (acción 11). El mecanismo de la fermentación sigue en Bachillerato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
-        <is>
-          <t>revisar</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>G03-CIE-U5-5.6, G03-CIE-U5-5.7, G03-CIE-U5-5.8, G03-CIE-U5-5.9, G03-CIE-U5-5.10, G03-CIE-U5-5.11, G03-CIE-U4-4.7, G03-CIE-U4-4.8, G03-CIE-U4-4.9</t>
-        </is>
-      </c>
-      <c r="D15" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="E15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>5. Los animales. / 4. Las plantas.</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="inlineStr">
-        <is>
-          <t>Sin redacción nueva: candidatos a consolidar si el MINED decide reducir el peso de Biología en 2.° a 4.°.</t>
-        </is>
-      </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>No aplica.</t>
-        </is>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>Invertebrados e insectos, Tropismos y hormonas vegetales</t>
-        </is>
-      </c>
-      <c r="K15" s="3" t="inlineStr">
-        <is>
-          <t>6 temas de 3.° sobre grupos de invertebrados (5.6 a 5.11); 3 temas sobre tropismos y nastias (4.7 a 4.9)</t>
-        </is>
-      </c>
-      <c r="L15" s="3" t="inlineStr">
         <is>
           <t>Repiten un mismo concepto con un detalle taxonómico o práctico alto para la edad. No se fusionan ahora porque el presupuesto ya cuadra. Quedan como opción si el MINED pasa horas a otras disciplinas (decisión abierta 1).</t>
         </is>
@@ -1332,7 +1290,7 @@
         <v>27</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="4">
         <f>C2-B2</f>
@@ -1378,7 +1336,7 @@
         <v>40</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="4">
         <f>C4-B4</f>

--- a/asignaturas/biologia/propuesta/Propuesta_Biologia_G02-G04.xlsx
+++ b/asignaturas/biologia/propuesta/Propuesta_Biologia_G02-G04.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -728,17 +728,17 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Inmunidad activa, pasiva y vacunas, Contagio y prevención de enfermedades, Tipos de patógenos</t>
+          <t>Contagio y prevención de enfermedades, Tipos de patógenos</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Inmunidad activa, pasiva y vacunas (2.°) necesita Sistema inmunitario (10.°), brecha 8; prerrequisito disponible: Tipos de patógenos (G03-6.1 y 6.3)</t>
+          <t>corregir_secuencia: Inmunidad activa, pasiva y vacunas (2.°) necesita Sistema inmunitario (10.°), brecha 8; el tema solo trabaja la vacuna como medida de prevención; prerrequisito disponible: Tipos de patógenos (G03-6.1 y 6.3)</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>En 2.° las vacunas llegan antes de que se sepa qué es un patógeno. En 3.° van después de infección y patógenos. El sistema inmunitario formal sigue en 10.° (decisión abierta 2).</t>
+          <t>En 2.° las vacunas llegan antes de que se sepa qué es un patógeno. En 3.° van después de infección y patógenos, como medida de prevención; la inmunidad activa y pasiva queda para Bachillerato, después del sistema inmunitario.</t>
         </is>
       </c>
     </row>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>Niveles de organización de los seres vivos</t>
+          <t>Niveles de organización ecológica</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>corregir_secuencia: Niveles de organización de los seres vivos (4.°) necesita La célula como unidad de la vida (6.°), brecha 2</t>
+          <t>corregir_secuencia: Niveles de organización de los seres vivos (4.°) necesita La célula como unidad de la vida (6.°), brecha 2; prerrequisitos disponibles: Factores bióticos y abióticos (G04-3.2) y Hábitat y ecosistemas comunes (2.°)</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>El tema trata la organización ecológica, que empieza en el organismo y no requiere la célula. Se precisa la redacción. La célula se adelanta en la propuesta 5.°–8.°.</t>
+          <t>El tema trata la organización ecológica, que empieza en el organismo y no requiere la célula. Se etiqueta con ese concepto y no con la escala célula-tejido-órgano, que sigue en 6.°.</t>
         </is>
       </c>
     </row>
@@ -1225,6 +1225,60 @@
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Repiten un mismo concepto con un detalle taxonómico o práctico alto para la edad. No se fusionan ahora porque el presupuesto ya cuadra. Quedan como opción si el MINED pasa horas a otras disciplinas (decisión abierta 1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>revisar</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>G04-CIE-U5-5.7</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>5. Cuerpo humano: materia y energía.</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>5.7. Relación del sistema circulatorio con los sistemas respiratorio y digestivo: la sangre lleva a todo el cuerpo el oxígeno y los nutrientes.</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>Traza en un esquema del cuerpo el recorrido de la sangre y señala dónde recoge el oxígeno y los nutrientes y adónde los lleva.</t>
+        </is>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Sistema circulatorio</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>corregir_secuencia: Niveles de organización de los seres vivos (4.°) necesita La célula como unidad de la vida (6.°), brecha 2; prerrequisito disponible: Sistema respiratorio (G04-5.3 y 5.4) y Sistema digestivo (G04-5.2)</t>
+        </is>
+      </c>
+      <c r="L15" s="3" t="inlineStr">
+        <is>
+          <t>El tema relaciona sistemas del cuerpo, no la escala célula-tejido-órgano-sistema, que exige la célula (6.°). Se redacta en términos de lo que la sangre transporta, sin costo de presupuesto.</t>
         </is>
       </c>
     </row>
